--- a/C/08. ADVANCED C FEATURES.xlsx
+++ b/C/08. ADVANCED C FEATURES.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12645" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="22260" windowHeight="12648" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Mục Lục" sheetId="1" r:id="rId1"/>
@@ -6901,14 +6901,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="13">
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
+  <fonts count="12">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -7067,12 +7060,12 @@
   </cellStyleXfs>
   <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -7081,56 +7074,56 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="2"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
     </xf>
   </cellXfs>
@@ -7414,10 +7407,10 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="B1:AC20"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="2:29" ht="15" thickBot="1"/>
-    <row r="2" spans="2:29" ht="24" thickBot="1">
+    <row r="1" spans="2:29" ht="14.4" thickBot="1"/>
+    <row r="2" spans="2:29" ht="23.4" thickBot="1">
       <c r="B2" s="1" t="s">
         <v>0</v>
       </c>
@@ -7435,7 +7428,7 @@
       <c r="N2" s="2"/>
       <c r="O2" s="3"/>
     </row>
-    <row r="3" spans="2:29" ht="17.25">
+    <row r="3" spans="2:29" ht="17.399999999999999">
       <c r="B3" s="4" t="s">
         <v>1</v>
       </c>
@@ -7446,7 +7439,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="4" spans="2:29" ht="15">
+    <row r="4" spans="2:29">
       <c r="B4" s="5" t="s">
         <v>4</v>
       </c>
@@ -7506,7 +7499,7 @@
       <c r="P9" s="5"/>
       <c r="AC9" s="5"/>
     </row>
-    <row r="10" spans="2:29" ht="15">
+    <row r="10" spans="2:29">
       <c r="B10" s="5" t="s">
         <v>19</v>
       </c>
@@ -7564,7 +7557,7 @@
     <row r="15" spans="2:29">
       <c r="B15" s="5"/>
     </row>
-    <row r="16" spans="2:29" ht="15">
+    <row r="16" spans="2:29">
       <c r="B16" s="5" t="s">
         <v>34</v>
       </c>
@@ -7597,22 +7590,22 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BF164"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="16384" width="3.125" style="9"/>
+    <col min="1" max="16384" width="3.09765625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:39" ht="15.75" thickBot="1">
+    <row r="1" spans="1:39" ht="14.4" thickBot="1">
       <c r="A1" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="2" spans="1:39" s="18" customFormat="1" ht="15.75" thickBot="1">
+    <row r="2" spans="1:39" s="18" customFormat="1" ht="14.4" thickBot="1">
       <c r="A2" s="17" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="3" spans="1:39" ht="15">
+    <row r="3" spans="1:39">
       <c r="A3" s="19" t="s">
         <v>132</v>
       </c>
@@ -7637,7 +7630,7 @@
       <c r="AL3" s="20"/>
       <c r="AM3" s="20"/>
     </row>
-    <row r="4" spans="1:39" ht="15">
+    <row r="4" spans="1:39">
       <c r="A4" s="7" t="s">
         <v>65</v>
       </c>
@@ -7645,7 +7638,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="5" spans="1:39" ht="15">
+    <row r="5" spans="1:39">
       <c r="A5" s="24" t="s">
         <v>205</v>
       </c>
@@ -7653,7 +7646,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="6" spans="1:39" ht="15">
+    <row r="6" spans="1:39">
       <c r="A6" s="14" t="s">
         <v>133</v>
       </c>
@@ -7661,7 +7654,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="8" spans="1:39" ht="15">
+    <row r="8" spans="1:39">
       <c r="A8" s="7" t="s">
         <v>66</v>
       </c>
@@ -7721,12 +7714,12 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:45" ht="15">
+    <row r="17" spans="1:45">
       <c r="AF17" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="18" spans="1:45" ht="15">
+    <row r="18" spans="1:45">
       <c r="A18" s="7" t="s">
         <v>71</v>
       </c>
@@ -7747,12 +7740,12 @@
         <v>134</v>
       </c>
     </row>
-    <row r="21" spans="1:45" ht="15">
+    <row r="21" spans="1:45">
       <c r="AF21" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="22" spans="1:45" ht="15">
+    <row r="22" spans="1:45">
       <c r="A22" s="7" t="s">
         <v>73</v>
       </c>
@@ -7760,7 +7753,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:45" ht="15">
+    <row r="23" spans="1:45">
       <c r="A23" s="11" t="s">
         <v>135</v>
       </c>
@@ -7773,7 +7766,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="25" spans="1:45" ht="15">
+    <row r="25" spans="1:45">
       <c r="B25" s="9" t="s">
         <v>202</v>
       </c>
@@ -7781,7 +7774,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="26" spans="1:45" ht="15">
+    <row r="26" spans="1:45">
       <c r="A26" s="7" t="s">
         <v>74</v>
       </c>
@@ -7799,7 +7792,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="30" spans="1:45" s="21" customFormat="1" ht="15">
+    <row r="30" spans="1:45" s="21" customFormat="1">
       <c r="A30" s="22" t="s">
         <v>143</v>
       </c>
@@ -7824,7 +7817,7 @@
       <c r="AR30" s="23"/>
       <c r="AS30" s="23"/>
     </row>
-    <row r="31" spans="1:45" ht="15">
+    <row r="31" spans="1:45">
       <c r="A31" s="7" t="s">
         <v>65</v>
       </c>
@@ -7832,7 +7825,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="32" spans="1:45" ht="15">
+    <row r="32" spans="1:45">
       <c r="A32" s="24" t="s">
         <v>204</v>
       </c>
@@ -7840,12 +7833,12 @@
         <v>203</v>
       </c>
     </row>
-    <row r="33" spans="1:33" ht="15">
+    <row r="33" spans="1:33" ht="14.4">
       <c r="AF33" s="8" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="34" spans="1:33" ht="15">
+    <row r="34" spans="1:33">
       <c r="A34" s="7" t="s">
         <v>66</v>
       </c>
@@ -7858,7 +7851,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="36" spans="1:33" ht="15">
+    <row r="36" spans="1:33">
       <c r="B36" s="12" t="s">
         <v>44</v>
       </c>
@@ -7926,7 +7919,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="46" spans="1:33" ht="15">
+    <row r="46" spans="1:33">
       <c r="A46" s="7" t="s">
         <v>71</v>
       </c>
@@ -7934,7 +7927,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="47" spans="1:33" ht="15">
+    <row r="47" spans="1:33">
       <c r="A47" s="11" t="s">
         <v>144</v>
       </c>
@@ -7950,7 +7943,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="50" spans="1:43" ht="15">
+    <row r="50" spans="1:43">
       <c r="A50" s="7" t="s">
         <v>73</v>
       </c>
@@ -7958,7 +7951,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="51" spans="1:43" ht="15">
+    <row r="51" spans="1:43">
       <c r="A51" s="11" t="s">
         <v>146</v>
       </c>
@@ -7971,13 +7964,13 @@
         <v>147</v>
       </c>
     </row>
-    <row r="54" spans="1:43" ht="15" thickBot="1"/>
-    <row r="55" spans="1:43" s="18" customFormat="1" ht="15.75" thickBot="1">
+    <row r="54" spans="1:43" ht="14.4" thickBot="1"/>
+    <row r="55" spans="1:43" s="18" customFormat="1" ht="14.4" thickBot="1">
       <c r="A55" s="17" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="56" spans="1:43" ht="15">
+    <row r="56" spans="1:43">
       <c r="A56" s="19" t="s">
         <v>87</v>
       </c>
@@ -8003,7 +7996,7 @@
       <c r="AP56" s="20"/>
       <c r="AQ56" s="20"/>
     </row>
-    <row r="57" spans="1:43" ht="15">
+    <row r="57" spans="1:43">
       <c r="A57" s="7" t="s">
         <v>65</v>
       </c>
@@ -8011,7 +8004,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="58" spans="1:43" ht="15">
+    <row r="58" spans="1:43">
       <c r="A58" s="24" t="s">
         <v>210</v>
       </c>
@@ -8019,7 +8012,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="59" spans="1:43" ht="15">
+    <row r="59" spans="1:43">
       <c r="A59" s="8" t="s">
         <v>153</v>
       </c>
@@ -8027,7 +8020,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="61" spans="1:43" ht="15">
+    <row r="61" spans="1:43">
       <c r="A61" s="7" t="s">
         <v>66</v>
       </c>
@@ -8070,7 +8063,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="67" spans="1:35" ht="15">
+    <row r="67" spans="1:35">
       <c r="A67" s="7" t="s">
         <v>71</v>
       </c>
@@ -8078,7 +8071,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="68" spans="1:35" ht="15">
+    <row r="68" spans="1:35">
       <c r="A68" s="11" t="s">
         <v>154</v>
       </c>
@@ -8097,7 +8090,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="71" spans="1:35" ht="15">
+    <row r="71" spans="1:35">
       <c r="A71" s="7" t="s">
         <v>91</v>
       </c>
@@ -8126,7 +8119,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="75" spans="1:35" ht="15">
+    <row r="75" spans="1:35">
       <c r="A75" s="7" t="s">
         <v>73</v>
       </c>
@@ -8134,7 +8127,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="76" spans="1:35" ht="15">
+    <row r="76" spans="1:35">
       <c r="A76" s="11" t="s">
         <v>156</v>
       </c>
@@ -8147,12 +8140,12 @@
         <v>94</v>
       </c>
     </row>
-    <row r="78" spans="1:35" ht="15">
+    <row r="78" spans="1:35">
       <c r="AH78" s="7" t="s">
         <v>71</v>
       </c>
     </row>
-    <row r="79" spans="1:35" ht="15">
+    <row r="79" spans="1:35">
       <c r="A79" s="7" t="s">
         <v>74</v>
       </c>
@@ -8160,7 +8153,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="80" spans="1:35" ht="15">
+    <row r="80" spans="1:35">
       <c r="A80" s="11" t="s">
         <v>157</v>
       </c>
@@ -8173,7 +8166,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="82" spans="1:34" ht="15">
+    <row r="82" spans="1:34">
       <c r="AH82" s="7" t="s">
         <v>91</v>
       </c>
@@ -8203,7 +8196,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="89" spans="1:34" ht="15">
+    <row r="89" spans="1:34">
       <c r="AH89" s="7" t="s">
         <v>73</v>
       </c>
@@ -8218,7 +8211,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="93" spans="1:34" ht="15">
+    <row r="93" spans="1:34">
       <c r="AH93" s="7" t="s">
         <v>74</v>
       </c>
@@ -8228,7 +8221,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="95" spans="1:34" ht="15">
+    <row r="95" spans="1:34">
       <c r="AH95" s="11" t="s">
         <v>164</v>
       </c>
@@ -8236,7 +8229,7 @@
     <row r="96" spans="1:34">
       <c r="AH96" s="11"/>
     </row>
-    <row r="97" spans="1:40" ht="15">
+    <row r="97" spans="1:40">
       <c r="A97" s="19" t="s">
         <v>54</v>
       </c>
@@ -8257,7 +8250,7 @@
       <c r="AM97" s="20"/>
       <c r="AN97" s="20"/>
     </row>
-    <row r="98" spans="1:40" ht="15">
+    <row r="98" spans="1:40">
       <c r="A98" s="7" t="s">
         <v>65</v>
       </c>
@@ -8265,7 +8258,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="99" spans="1:40" ht="15">
+    <row r="99" spans="1:40">
       <c r="A99" s="24" t="s">
         <v>211</v>
       </c>
@@ -8273,7 +8266,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="101" spans="1:40" ht="15">
+    <row r="101" spans="1:40">
       <c r="A101" s="7" t="s">
         <v>105</v>
       </c>
@@ -8308,7 +8301,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="106" spans="1:40" ht="15">
+    <row r="106" spans="1:40">
       <c r="A106" s="12" t="s">
         <v>107</v>
       </c>
@@ -8324,17 +8317,17 @@
         <v>115</v>
       </c>
     </row>
-    <row r="108" spans="1:40" ht="15">
+    <row r="108" spans="1:40">
       <c r="AG108" s="11" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="109" spans="1:40" ht="15">
+    <row r="109" spans="1:40">
       <c r="A109" s="7" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="110" spans="1:40" ht="15">
+    <row r="110" spans="1:40">
       <c r="A110" s="8" t="s">
         <v>165</v>
       </c>
@@ -8342,7 +8335,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="111" spans="1:40" ht="15">
+    <row r="111" spans="1:40">
       <c r="A111" s="8" t="s">
         <v>166</v>
       </c>
@@ -8350,7 +8343,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="113" spans="1:58" ht="15">
+    <row r="113" spans="1:58">
       <c r="A113" s="7" t="s">
         <v>91</v>
       </c>
@@ -8370,22 +8363,22 @@
         <v>41</v>
       </c>
     </row>
-    <row r="118" spans="1:58" ht="15">
+    <row r="118" spans="1:58">
       <c r="A118" s="7" t="s">
         <v>73</v>
       </c>
     </row>
-    <row r="119" spans="1:58" ht="15">
+    <row r="119" spans="1:58">
       <c r="A119" s="11" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="120" spans="1:58" ht="15">
+    <row r="120" spans="1:58">
       <c r="A120" s="11" t="s">
         <v>168</v>
       </c>
     </row>
-    <row r="122" spans="1:58" ht="15">
+    <row r="122" spans="1:58">
       <c r="A122" s="7" t="s">
         <v>85</v>
       </c>
@@ -8395,13 +8388,13 @@
         <v>111</v>
       </c>
     </row>
-    <row r="124" spans="1:58" ht="15" thickBot="1"/>
-    <row r="125" spans="1:58" s="18" customFormat="1" ht="15.75" thickBot="1">
+    <row r="124" spans="1:58" ht="14.4" thickBot="1"/>
+    <row r="125" spans="1:58" s="18" customFormat="1" ht="14.4" thickBot="1">
       <c r="A125" s="17" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="126" spans="1:58" ht="15">
+    <row r="126" spans="1:58">
       <c r="A126" s="19" t="s">
         <v>61</v>
       </c>
@@ -8434,7 +8427,7 @@
       <c r="BE126" s="20"/>
       <c r="BF126" s="20"/>
     </row>
-    <row r="127" spans="1:58" ht="15">
+    <row r="127" spans="1:58">
       <c r="A127" s="7" t="s">
         <v>117</v>
       </c>
@@ -8445,7 +8438,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="128" spans="1:58" ht="15">
+    <row r="128" spans="1:58">
       <c r="A128" s="11" t="s">
         <v>171</v>
       </c>
@@ -8456,7 +8449,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="129" spans="1:44" ht="15">
+    <row r="129" spans="1:44">
       <c r="A129" s="11" t="s">
         <v>172</v>
       </c>
@@ -8472,7 +8465,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="131" spans="1:44" ht="15">
+    <row r="131" spans="1:44">
       <c r="U131" s="7" t="s">
         <v>118</v>
       </c>
@@ -8480,7 +8473,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="132" spans="1:44" ht="15">
+    <row r="132" spans="1:44">
       <c r="A132" s="7" t="s">
         <v>118</v>
       </c>
@@ -8555,7 +8548,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="140" spans="1:44" ht="15">
+    <row r="140" spans="1:44">
       <c r="A140" s="7" t="s">
         <v>85</v>
       </c>
@@ -8563,7 +8556,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="141" spans="1:44" ht="15">
+    <row r="141" spans="1:44">
       <c r="A141" s="11" t="s">
         <v>174</v>
       </c>
@@ -8579,7 +8572,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="143" spans="1:44" ht="15">
+    <row r="143" spans="1:44">
       <c r="A143" s="19" t="s">
         <v>62</v>
       </c>
@@ -8594,7 +8587,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="144" spans="1:44" ht="15">
+    <row r="144" spans="1:44">
       <c r="A144" s="7" t="s">
         <v>117</v>
       </c>
@@ -8602,7 +8595,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="145" spans="1:44" ht="15">
+    <row r="145" spans="1:44">
       <c r="A145" s="11" t="s">
         <v>175</v>
       </c>
@@ -8618,7 +8611,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="148" spans="1:44" ht="15">
+    <row r="148" spans="1:44">
       <c r="A148" s="7" t="s">
         <v>73</v>
       </c>
@@ -8628,8 +8621,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="150" spans="1:44" ht="15" thickBot="1"/>
-    <row r="151" spans="1:44" s="18" customFormat="1" ht="15.75" thickBot="1">
+    <row r="150" spans="1:44" ht="14.4" thickBot="1"/>
+    <row r="151" spans="1:44" s="18" customFormat="1" ht="14.4" thickBot="1">
       <c r="A151" s="17" t="s">
         <v>129</v>
       </c>
@@ -8637,7 +8630,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="152" spans="1:44" ht="15">
+    <row r="152" spans="1:44">
       <c r="A152" s="8" t="s">
         <v>183</v>
       </c>
@@ -8645,7 +8638,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="153" spans="1:44" ht="15">
+    <row r="153" spans="1:44">
       <c r="A153" s="15" t="s">
         <v>184</v>
       </c>
@@ -8653,19 +8646,19 @@
         <v>193</v>
       </c>
     </row>
-    <row r="154" spans="1:44" ht="15">
+    <row r="154" spans="1:44">
       <c r="A154" s="11"/>
       <c r="AA154" s="15" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="155" spans="1:44" ht="15">
+    <row r="155" spans="1:44">
       <c r="A155" s="8" t="s">
         <v>185</v>
       </c>
       <c r="AA155" s="11"/>
     </row>
-    <row r="156" spans="1:44" ht="15">
+    <row r="156" spans="1:44">
       <c r="A156" s="16" t="s">
         <v>186</v>
       </c>
@@ -8673,19 +8666,19 @@
         <v>195</v>
       </c>
     </row>
-    <row r="157" spans="1:44" ht="15">
+    <row r="157" spans="1:44">
       <c r="A157" s="11"/>
       <c r="AA157" s="15" t="s">
         <v>196</v>
       </c>
     </row>
-    <row r="158" spans="1:44" ht="15">
+    <row r="158" spans="1:44">
       <c r="A158" s="8" t="s">
         <v>187</v>
       </c>
       <c r="AA158" s="11"/>
     </row>
-    <row r="159" spans="1:44" ht="15">
+    <row r="159" spans="1:44">
       <c r="A159" s="16" t="s">
         <v>188</v>
       </c>
@@ -8693,19 +8686,19 @@
         <v>197</v>
       </c>
     </row>
-    <row r="160" spans="1:44" ht="15">
+    <row r="160" spans="1:44">
       <c r="A160" s="11"/>
       <c r="AA160" s="15" t="s">
         <v>198</v>
       </c>
     </row>
-    <row r="161" spans="1:27" ht="15">
+    <row r="161" spans="1:27">
       <c r="A161" s="8" t="s">
         <v>189</v>
       </c>
       <c r="AA161" s="11"/>
     </row>
-    <row r="162" spans="1:27" ht="15">
+    <row r="162" spans="1:27">
       <c r="A162" s="15" t="s">
         <v>130</v>
       </c>
@@ -8713,7 +8706,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="163" spans="1:27" ht="15">
+    <row r="163" spans="1:27">
       <c r="A163" s="15" t="s">
         <v>190</v>
       </c>
@@ -8735,22 +8728,22 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:AG118"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
   <cols>
-    <col min="1" max="16384" width="3.125" style="9"/>
+    <col min="1" max="16384" width="3.09765625" style="9"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:31" ht="15.75" thickBot="1">
+    <row r="1" spans="1:31" ht="14.4" thickBot="1">
       <c r="A1" s="10" t="s">
         <v>213</v>
       </c>
     </row>
-    <row r="2" spans="1:31" s="18" customFormat="1" ht="15.75" thickBot="1">
+    <row r="2" spans="1:31" s="18" customFormat="1" ht="14.4" thickBot="1">
       <c r="A2" s="17" t="s">
         <v>214</v>
       </c>
     </row>
-    <row r="3" spans="1:31" ht="15">
+    <row r="3" spans="1:31">
       <c r="A3" s="19" t="s">
         <v>286</v>
       </c>
@@ -8771,7 +8764,7 @@
       <c r="AD3" s="20"/>
       <c r="AE3" s="20"/>
     </row>
-    <row r="4" spans="1:31" ht="15">
+    <row r="4" spans="1:31">
       <c r="A4" s="7" t="s">
         <v>65</v>
       </c>
@@ -8787,7 +8780,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="6" spans="1:31" ht="15">
+    <row r="6" spans="1:31">
       <c r="A6" s="24" t="s">
         <v>215</v>
       </c>
@@ -8800,7 +8793,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="8" spans="1:31" ht="15">
+    <row r="8" spans="1:31">
       <c r="A8" s="7" t="s">
         <v>66</v>
       </c>
@@ -8856,7 +8849,7 @@
         <v>219</v>
       </c>
     </row>
-    <row r="16" spans="1:31" ht="15">
+    <row r="16" spans="1:31">
       <c r="A16" s="12" t="s">
         <v>41</v>
       </c>
@@ -8869,7 +8862,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="18" spans="1:26" ht="15">
+    <row r="18" spans="1:26">
       <c r="A18" s="7" t="s">
         <v>71</v>
       </c>
@@ -8883,7 +8876,7 @@
       </c>
       <c r="Z19" s="13"/>
     </row>
-    <row r="20" spans="1:26" ht="15">
+    <row r="20" spans="1:26">
       <c r="A20" s="11" t="s">
         <v>288</v>
       </c>
@@ -8896,7 +8889,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="22" spans="1:26" ht="15">
+    <row r="22" spans="1:26">
       <c r="A22" s="7" t="s">
         <v>73</v>
       </c>
@@ -8923,7 +8916,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="26" spans="1:26" ht="15">
+    <row r="26" spans="1:26">
       <c r="A26" s="7" t="s">
         <v>221</v>
       </c>
@@ -8931,7 +8924,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="27" spans="1:26" ht="15">
+    <row r="27" spans="1:26">
       <c r="A27" s="11" t="s">
         <v>290</v>
       </c>
@@ -8954,22 +8947,22 @@
         <v>41</v>
       </c>
     </row>
-    <row r="32" spans="1:26" ht="15">
+    <row r="32" spans="1:26">
       <c r="Y32" s="7" t="s">
         <v>232</v>
       </c>
     </row>
-    <row r="33" spans="1:30" ht="15">
+    <row r="33" spans="1:30">
       <c r="Y33" s="11" t="s">
         <v>298</v>
       </c>
     </row>
-    <row r="34" spans="1:30" ht="15">
+    <row r="34" spans="1:30">
       <c r="Y34" s="11" t="s">
         <v>299</v>
       </c>
     </row>
-    <row r="36" spans="1:30" ht="15">
+    <row r="36" spans="1:30">
       <c r="A36" s="19" t="s">
         <v>233</v>
       </c>
@@ -8988,7 +8981,7 @@
       <c r="AC36" s="20"/>
       <c r="AD36" s="20"/>
     </row>
-    <row r="37" spans="1:30" ht="15">
+    <row r="37" spans="1:30">
       <c r="A37" s="7" t="s">
         <v>65</v>
       </c>
@@ -8996,7 +8989,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="38" spans="1:30" ht="15">
+    <row r="38" spans="1:30">
       <c r="A38" s="24" t="s">
         <v>325</v>
       </c>
@@ -9012,7 +9005,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="41" spans="1:30" ht="15">
+    <row r="41" spans="1:30">
       <c r="A41" s="7" t="s">
         <v>66</v>
       </c>
@@ -9053,7 +9046,7 @@
     <row r="46" spans="1:30">
       <c r="B46" s="13"/>
     </row>
-    <row r="47" spans="1:30" ht="15">
+    <row r="47" spans="1:30">
       <c r="B47" s="12" t="s">
         <v>68</v>
       </c>
@@ -9088,7 +9081,7 @@
         <v>246</v>
       </c>
     </row>
-    <row r="52" spans="1:26" ht="15">
+    <row r="52" spans="1:26">
       <c r="A52" s="7" t="s">
         <v>239</v>
       </c>
@@ -9123,7 +9116,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="57" spans="1:26" ht="15">
+    <row r="57" spans="1:26">
       <c r="A57" s="7" t="s">
         <v>73</v>
       </c>
@@ -9147,7 +9140,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="1:26" ht="15">
+    <row r="61" spans="1:26">
       <c r="Y61" s="7" t="s">
         <v>73</v>
       </c>
@@ -9157,17 +9150,17 @@
         <v>308</v>
       </c>
     </row>
-    <row r="63" spans="1:26" ht="15" thickBot="1">
+    <row r="63" spans="1:26" ht="14.4" thickBot="1">
       <c r="Y63" s="11" t="s">
         <v>252</v>
       </c>
     </row>
-    <row r="64" spans="1:26" s="18" customFormat="1" ht="15.75" thickBot="1">
+    <row r="64" spans="1:26" s="18" customFormat="1" ht="14.4" thickBot="1">
       <c r="A64" s="17" t="s">
         <v>253</v>
       </c>
     </row>
-    <row r="65" spans="1:33" ht="15">
+    <row r="65" spans="1:33">
       <c r="A65" s="19" t="s">
         <v>309</v>
       </c>
@@ -9188,7 +9181,7 @@
       <c r="AF65" s="20"/>
       <c r="AG65" s="20"/>
     </row>
-    <row r="66" spans="1:33" ht="15">
+    <row r="66" spans="1:33">
       <c r="A66" s="7" t="s">
         <v>65</v>
       </c>
@@ -9196,7 +9189,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="67" spans="1:33" ht="15">
+    <row r="67" spans="1:33">
       <c r="A67" s="24" t="s">
         <v>254</v>
       </c>
@@ -9204,7 +9197,7 @@
         <v>327</v>
       </c>
     </row>
-    <row r="68" spans="1:33" ht="15">
+    <row r="68" spans="1:33">
       <c r="A68" s="24" t="s">
         <v>255</v>
       </c>
@@ -9217,7 +9210,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="70" spans="1:33" ht="15">
+    <row r="70" spans="1:33">
       <c r="A70" s="7" t="s">
         <v>256</v>
       </c>
@@ -9238,7 +9231,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="73" spans="1:33" ht="15">
+    <row r="73" spans="1:33">
       <c r="A73" s="7" t="s">
         <v>73</v>
       </c>
@@ -9265,7 +9258,7 @@
     <row r="76" spans="1:33">
       <c r="Y76" s="13"/>
     </row>
-    <row r="77" spans="1:33" ht="15">
+    <row r="77" spans="1:33">
       <c r="A77" s="7" t="s">
         <v>221</v>
       </c>
@@ -9291,7 +9284,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="82" spans="1:33" ht="15">
+    <row r="82" spans="1:33">
       <c r="Y82" s="7" t="s">
         <v>73</v>
       </c>
@@ -9309,7 +9302,7 @@
     <row r="85" spans="1:33">
       <c r="Y85" s="11"/>
     </row>
-    <row r="86" spans="1:33" ht="15">
+    <row r="86" spans="1:33">
       <c r="A86" s="19" t="s">
         <v>272</v>
       </c>
@@ -9335,7 +9328,7 @@
       <c r="AF86" s="20"/>
       <c r="AG86" s="20"/>
     </row>
-    <row r="87" spans="1:33" ht="15">
+    <row r="87" spans="1:33">
       <c r="A87" s="7" t="s">
         <v>65</v>
       </c>
@@ -9367,7 +9360,7 @@
       </c>
       <c r="B90" s="26"/>
     </row>
-    <row r="91" spans="1:33" ht="15">
+    <row r="91" spans="1:33">
       <c r="A91" s="11"/>
       <c r="X91" s="7" t="s">
         <v>118</v>
@@ -9408,7 +9401,7 @@
         <v>280</v>
       </c>
     </row>
-    <row r="97" spans="1:25" ht="15">
+    <row r="97" spans="1:25">
       <c r="A97" s="7" t="s">
         <v>118</v>
       </c>
@@ -9435,7 +9428,7 @@
     <row r="100" spans="1:25">
       <c r="B100" s="13"/>
     </row>
-    <row r="101" spans="1:25" ht="15">
+    <row r="101" spans="1:25">
       <c r="B101" s="12" t="s">
         <v>275</v>
       </c>
@@ -9443,7 +9436,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="102" spans="1:25" ht="15">
+    <row r="102" spans="1:25">
       <c r="B102" s="12" t="s">
         <v>276</v>
       </c>
@@ -9462,7 +9455,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="105" spans="1:25" ht="15">
+    <row r="105" spans="1:25">
       <c r="B105" s="12" t="s">
         <v>277</v>
       </c>
@@ -9483,7 +9476,7 @@
         <v>318</v>
       </c>
     </row>
-    <row r="109" spans="1:25" ht="15">
+    <row r="109" spans="1:25">
       <c r="A109" s="7" t="s">
         <v>73</v>
       </c>
@@ -9498,7 +9491,7 @@
         <v>315</v>
       </c>
     </row>
-    <row r="113" spans="1:28" ht="15">
+    <row r="113" spans="1:28">
       <c r="A113" s="10" t="s">
         <v>284</v>
       </c>
@@ -9506,7 +9499,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="114" spans="1:28" ht="15">
+    <row r="114" spans="1:28">
       <c r="A114" s="24" t="s">
         <v>332</v>
       </c>
@@ -9515,7 +9508,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="115" spans="1:28" ht="15">
+    <row r="115" spans="1:28">
       <c r="A115" s="24" t="s">
         <v>333</v>
       </c>
@@ -9524,7 +9517,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="116" spans="1:28" ht="15">
+    <row r="116" spans="1:28">
       <c r="A116" s="24" t="s">
         <v>334</v>
       </c>
@@ -9533,7 +9526,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="117" spans="1:28" ht="15">
+    <row r="117" spans="1:28">
       <c r="A117" s="24" t="s">
         <v>335</v>
       </c>
@@ -9542,7 +9535,7 @@
         <v>322</v>
       </c>
     </row>
-    <row r="118" spans="1:28" ht="15">
+    <row r="118" spans="1:28">
       <c r="A118" s="24" t="s">
         <v>336</v>
       </c>
@@ -9559,19 +9552,19 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:BG108"/>
-  <sheetFormatPr defaultColWidth="3.125" defaultRowHeight="14.25"/>
+  <sheetFormatPr defaultColWidth="3.09765625" defaultRowHeight="13.8"/>
   <sheetData>
-    <row r="1" spans="1:59" s="9" customFormat="1" ht="15.75" thickBot="1">
+    <row r="1" spans="1:59" s="9" customFormat="1" ht="14.4" thickBot="1">
       <c r="A1" s="10" t="s">
         <v>337</v>
       </c>
     </row>
-    <row r="2" spans="1:59" s="18" customFormat="1" ht="15.75" thickBot="1">
+    <row r="2" spans="1:59" s="18" customFormat="1" ht="14.4" thickBot="1">
       <c r="A2" s="17" t="s">
         <v>338</v>
       </c>
     </row>
-    <row r="3" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="3" spans="1:59" s="9" customFormat="1">
       <c r="A3" s="19" t="s">
         <v>339</v>
       </c>
@@ -9610,7 +9603,7 @@
       <c r="BF3" s="20"/>
       <c r="BG3" s="20"/>
     </row>
-    <row r="4" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="4" spans="1:59" s="9" customFormat="1">
       <c r="A4" s="7" t="s">
         <v>340</v>
       </c>
@@ -9624,7 +9617,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="5" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="5" spans="1:59" s="9" customFormat="1">
       <c r="A5" s="24" t="s">
         <v>442</v>
       </c>
@@ -9639,7 +9632,7 @@
       </c>
       <c r="BB5" s="26"/>
     </row>
-    <row r="6" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="6" spans="1:59" s="9" customFormat="1">
       <c r="A6" s="24" t="s">
         <v>341</v>
       </c>
@@ -9650,12 +9643,12 @@
         <v>444</v>
       </c>
     </row>
-    <row r="7" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="7" spans="1:59" s="9" customFormat="1">
       <c r="BA7" s="7" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="8" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="8" spans="1:59" s="9" customFormat="1">
       <c r="A8" s="7" t="s">
         <v>118</v>
       </c>
@@ -9690,7 +9683,7 @@
       <c r="T10" s="13"/>
       <c r="AJ10" s="13"/>
     </row>
-    <row r="11" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="11" spans="1:59" s="9" customFormat="1">
       <c r="B11" s="12" t="s">
         <v>343</v>
       </c>
@@ -9767,7 +9760,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="1:53" s="9" customFormat="1" ht="15">
+    <row r="17" spans="1:53" s="9" customFormat="1">
       <c r="B17" s="12" t="s">
         <v>347</v>
       </c>
@@ -9801,7 +9794,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="20" spans="1:53" s="9" customFormat="1" ht="15">
+    <row r="20" spans="1:53" s="9" customFormat="1">
       <c r="T20" s="12" t="s">
         <v>361</v>
       </c>
@@ -9809,7 +9802,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="21" spans="1:53" s="9" customFormat="1" ht="15">
+    <row r="21" spans="1:53" s="9" customFormat="1">
       <c r="A21" s="7" t="s">
         <v>348</v>
       </c>
@@ -9857,7 +9850,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="24" spans="1:53" s="9" customFormat="1" ht="15">
+    <row r="24" spans="1:53" s="9" customFormat="1">
       <c r="T24" s="7" t="s">
         <v>73</v>
       </c>
@@ -9865,7 +9858,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="25" spans="1:53" s="9" customFormat="1" ht="15">
+    <row r="25" spans="1:53" s="9" customFormat="1">
       <c r="A25" s="7" t="s">
         <v>73</v>
       </c>
@@ -9892,7 +9885,7 @@
         <v>350</v>
       </c>
     </row>
-    <row r="28" spans="1:53" s="9" customFormat="1" ht="15">
+    <row r="28" spans="1:53" s="9" customFormat="1">
       <c r="T28" s="7" t="s">
         <v>221</v>
       </c>
@@ -9900,7 +9893,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="29" spans="1:53" s="9" customFormat="1" ht="15">
+    <row r="29" spans="1:53" s="9" customFormat="1">
       <c r="A29" s="7" t="s">
         <v>221</v>
       </c>
@@ -9911,7 +9904,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="30" spans="1:53" s="9" customFormat="1" ht="15">
+    <row r="30" spans="1:53" s="9" customFormat="1">
       <c r="A30" s="11" t="s">
         <v>351</v>
       </c>
@@ -9927,13 +9920,13 @@
         <v>352</v>
       </c>
     </row>
-    <row r="32" spans="1:53" s="9" customFormat="1" ht="15" thickBot="1"/>
-    <row r="33" spans="1:59" s="18" customFormat="1" ht="15.75" thickBot="1">
+    <row r="32" spans="1:53" s="9" customFormat="1" ht="14.4" thickBot="1"/>
+    <row r="33" spans="1:59" s="18" customFormat="1" ht="14.4" thickBot="1">
       <c r="A33" s="17" t="s">
         <v>384</v>
       </c>
     </row>
-    <row r="34" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="34" spans="1:59" s="9" customFormat="1">
       <c r="A34" s="19" t="s">
         <v>385</v>
       </c>
@@ -9974,7 +9967,7 @@
       <c r="BF34" s="20"/>
       <c r="BG34" s="20"/>
     </row>
-    <row r="35" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="35" spans="1:59" s="9" customFormat="1">
       <c r="A35" s="7" t="s">
         <v>340</v>
       </c>
@@ -9988,7 +9981,7 @@
         <v>340</v>
       </c>
     </row>
-    <row r="36" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="36" spans="1:59" s="9" customFormat="1">
       <c r="A36" s="24" t="s">
         <v>447</v>
       </c>
@@ -10007,7 +10000,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="38" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="38" spans="1:59" s="9" customFormat="1">
       <c r="T38" s="7" t="s">
         <v>256</v>
       </c>
@@ -10018,7 +10011,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="39" spans="1:59" s="9" customFormat="1">
       <c r="A39" s="7" t="s">
         <v>118</v>
       </c>
@@ -10071,7 +10064,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="43" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="43" spans="1:59" s="9" customFormat="1">
       <c r="A43" s="7" t="s">
         <v>73</v>
       </c>
@@ -10080,7 +10073,7 @@
       </c>
       <c r="BB43" s="11"/>
     </row>
-    <row r="44" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="44" spans="1:59" s="9" customFormat="1">
       <c r="A44" s="11" t="s">
         <v>439</v>
       </c>
@@ -10091,7 +10084,7 @@
         <v>427</v>
       </c>
     </row>
-    <row r="45" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="45" spans="1:59" s="9" customFormat="1">
       <c r="A45" s="9" t="s">
         <v>440</v>
       </c>
@@ -10122,7 +10115,7 @@
         <v>403</v>
       </c>
     </row>
-    <row r="48" spans="1:59" s="9" customFormat="1" ht="15">
+    <row r="48" spans="1:59" s="9" customFormat="1">
       <c r="T48" s="12" t="s">
         <v>397</v>
       </c>
@@ -10138,12 +10131,12 @@
         <v>429</v>
       </c>
     </row>
-    <row r="50" spans="1:54" s="9" customFormat="1" ht="15" thickBot="1">
+    <row r="50" spans="1:54" s="9" customFormat="1" ht="14.4" thickBot="1">
       <c r="BB50" s="11" t="s">
         <v>430</v>
       </c>
     </row>
-    <row r="51" spans="1:54" s="18" customFormat="1" ht="15.75" thickBot="1">
+    <row r="51" spans="1:54" s="18" customFormat="1" ht="14.4" thickBot="1">
       <c r="A51" s="17" t="s">
         <v>409</v>
       </c>
@@ -10151,7 +10144,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="52" spans="1:54" s="9" customFormat="1" ht="15">
+    <row r="52" spans="1:54" s="9" customFormat="1">
       <c r="A52" s="8" t="s">
         <v>431</v>
       </c>
@@ -10159,7 +10152,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="53" spans="1:54" s="9" customFormat="1" ht="15">
+    <row r="53" spans="1:54" s="9" customFormat="1">
       <c r="A53" s="8" t="s">
         <v>432</v>
       </c>
@@ -10167,7 +10160,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="54" spans="1:54" s="9" customFormat="1" ht="15">
+    <row r="54" spans="1:54" s="9" customFormat="1">
       <c r="A54" s="8" t="s">
         <v>433</v>
       </c>
@@ -10175,7 +10168,7 @@
         <v>437</v>
       </c>
     </row>
-    <row r="55" spans="1:54" s="9" customFormat="1" ht="15">
+    <row r="55" spans="1:54" s="9" customFormat="1">
       <c r="A55" s="11" t="s">
         <v>410</v>
       </c>
